--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.191270410545737</v>
+        <v>1.201084788396404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05297788398706858</v>
+        <v>0.06561127440989961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb2Se3</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -468,10 +468,154 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.110128237447043</v>
+        <v>1.112809405129241</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01071939767468418</v>
+        <v>0.01659379514747156</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sb300</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.196451458058087</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05982312878776436</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sb300</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.104671720995331</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01480100232682815</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sb400</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.191277916771089</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05664919135416005</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sb400</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.111695526525509</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.01250735627449241</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400deg_400Sb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.193324303829811</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05558177663419467</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>400deg_400Sb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.108950251881352</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01173705220567998</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>room_400Sb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.180118245295819</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.04027390564612535</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>room_400Sb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.108052245480439</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01756367651926552</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb200</t>
+          <t>Mo_25Se_200Sb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.201084788396404</v>
+        <v>1.227474440790137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06561127440989961</v>
+        <v>0.010592874544675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb200</t>
+          <t>Mo_25Se_200Sb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.112809405129241</v>
+        <v>0.9906569807286888</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01659379514747156</v>
+        <v>0.01562100022764621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sb300</t>
+          <t>Mo_125Se_200Sb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -486,16 +486,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.196451458058087</v>
+        <v>1.134629018804752</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05982312878776436</v>
+        <v>0.02335454364426821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sb300</t>
+          <t>Mo_125Se_200Sb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.104671720995331</v>
+        <v>0.8897474050259655</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01480100232682815</v>
+        <v>0.03023388822630804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sb400</t>
+          <t>Mo_25Se_300Sb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.191277916771089</v>
+        <v>1.294894899381495</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05664919135416005</v>
+        <v>0.02372869622460992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sb400</t>
+          <t>Mo_25Se_300Sb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.111695526525509</v>
+        <v>0.9930569202440097</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01250735627449241</v>
+        <v>0.008793552788345298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>400deg_400Sb</t>
+          <t>Mo_125Se_300Sb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.193324303829811</v>
+        <v>1.333977176300491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05558177663419467</v>
+        <v>0.02889590630441228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>400deg_400Sb</t>
+          <t>Mo_125Se_300Sb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.108950251881352</v>
+        <v>1.047598390089843</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01173705220567998</v>
+        <v>0.009375548227668278</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>room_400Sb</t>
+          <t>Mo_25Se_400Sb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.180118245295819</v>
+        <v>1.25825672325223</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04027390564612535</v>
+        <v>0.01288940790982117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>room_400Sb</t>
+          <t>Mo_25Se_400Sb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -612,10 +612,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.108052245480439</v>
+        <v>1.038327700222461</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01756367651926552</v>
+        <v>0.02246763575534751</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mo_125Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.329359488209254</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02616818371377388</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mo_125Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.03499525750713</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01079799631171316</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mo_25Se_200Sb</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.227474440790137</v>
+        <v>1.338880994112401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.010592874544675</v>
+        <v>0.03388430248268661</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mo_25Se_200Sb</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9906569807286888</v>
+        <v>1.112809405129241</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01562100022764621</v>
+        <v>0.01424013453348423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mo_125Se_200Sb</t>
+          <t>Sb300</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -486,16 +486,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.134629018804752</v>
+        <v>1.33637689328179</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02335454364426821</v>
+        <v>0.02946769041993213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mo_125Se_200Sb</t>
+          <t>Sb300</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8897474050259655</v>
+        <v>1.104671720995331</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03023388822630804</v>
+        <v>0.0163961169254037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mo_25Se_300Sb</t>
+          <t>Sb400</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.294894899381495</v>
+        <v>1.312485296838778</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02372869622460992</v>
+        <v>0.01933445381648919</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mo_25Se_300Sb</t>
+          <t>Sb400</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9930569202440097</v>
+        <v>1.111695526525509</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008793552788345298</v>
+        <v>0.02517261278613037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mo_125Se_300Sb</t>
+          <t>Mo_25Se_200Sb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.333977176300491</v>
+        <v>1.227474440790137</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02889590630441228</v>
+        <v>0.010592874544675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mo_125Se_300Sb</t>
+          <t>Mo_25Se_200Sb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.047598390089843</v>
+        <v>0.9906569807286888</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009375548227668278</v>
+        <v>0.01562100022764621</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mo_25Se_400Sb</t>
+          <t>Mo_125Se_200Sb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.25825672325223</v>
+        <v>1.134629018804752</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01288940790982117</v>
+        <v>0.02335454364426821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mo_25Se_400Sb</t>
+          <t>Mo_125Se_200Sb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.038327700222461</v>
+        <v>0.8897474050259655</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02246763575534751</v>
+        <v>0.03023388822630804</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mo_125Se_400Sb</t>
+          <t>Mo_25Se_300Sb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -630,27 +630,135 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.329359488209254</v>
+        <v>1.294894899381495</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02616818371377388</v>
+        <v>0.02372869622460992</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Mo_25Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9930569202440097</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.008793552788345298</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mo_125Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.333977176300491</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.02889590630441228</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mo_125Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.047598390089843</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.009375548227668278</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mo_25Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.25825672325223</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01288940790982117</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mo_25Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.038327700222461</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.02246763575534751</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Mo_125Se_400Sb</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.329359488209254</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.02616818371377388</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mo_125Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>1.03499525750713</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D19" t="n">
         <v>0.01079799631171316</v>
       </c>
     </row>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.338880994112401</v>
+        <v>1.201084788396404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03388430248268661</v>
+        <v>0.09594243273782281</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>1.112809405129241</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01424013453348423</v>
+        <v>0.05358192065359806</v>
       </c>
     </row>
     <row r="4">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.33637689328179</v>
+        <v>1.196451458058087</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02946769041993213</v>
+        <v>0.09106605469441002</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>1.104671720995331</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0163961169254037</v>
+        <v>0.05089960295758991</v>
       </c>
     </row>
     <row r="6">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.312485296838778</v>
+        <v>1.191277916771089</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01933445381648919</v>
+        <v>0.09102351330055976</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>1.111695526525509</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02517261278613037</v>
+        <v>0.04921159029328564</v>
       </c>
     </row>
     <row r="8">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.227474440790137</v>
+        <v>1.129801596051832</v>
       </c>
       <c r="D8" t="n">
-        <v>0.010592874544675</v>
+        <v>0.0412271176589978</v>
       </c>
     </row>
     <row r="9">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9906569807286888</v>
+        <v>0.9860919956939599</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01562100022764621</v>
+        <v>0.0232035051469779</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         <v>1.134629018804752</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02335454364426821</v>
+        <v>0.06335461504731341</v>
       </c>
     </row>
     <row r="11">
@@ -615,7 +615,7 @@
         <v>0.8897474050259655</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03023388822630804</v>
+        <v>0.04254422120919129</v>
       </c>
     </row>
     <row r="12">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.294894899381495</v>
+        <v>1.170478039530471</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02372869622460992</v>
+        <v>0.06841814052637445</v>
       </c>
     </row>
     <row r="13">
@@ -651,7 +651,7 @@
         <v>0.9930569202440097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.008793552788345298</v>
+        <v>0.04308117309271923</v>
       </c>
     </row>
     <row r="14">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.333977176300491</v>
+        <v>1.184143034864894</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02889590630441228</v>
+        <v>0.0780094018372882</v>
       </c>
     </row>
     <row r="15">
@@ -687,7 +687,7 @@
         <v>1.047598390089843</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009375548227668278</v>
+        <v>0.04900609120275409</v>
       </c>
     </row>
     <row r="16">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.25825672325223</v>
+        <v>1.180588721930234</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01288940790982117</v>
+        <v>0.07196233614548796</v>
       </c>
     </row>
     <row r="17">
@@ -723,7 +723,7 @@
         <v>1.038327700222461</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02246763575534751</v>
+        <v>0.04238852094206078</v>
       </c>
     </row>
     <row r="18">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.329359488209254</v>
+        <v>1.182185036955623</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02616818371377388</v>
+        <v>0.07090771464597762</v>
       </c>
     </row>
     <row r="19">
@@ -759,7 +759,7 @@
         <v>1.03499525750713</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01079799631171316</v>
+        <v>0.04085617909626622</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,16 +432,11 @@
           <t>Gap (eV)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Error (eV)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sb200</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -450,16 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.201084788396404</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.09594243273782281</v>
+        <v>2.238377246593132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sb200</t>
+          <t>CdS1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -468,16 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.112809405129241</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.05358192065359806</v>
+        <v>1.424397396537707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sb300</t>
+          <t>CdS2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -486,16 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.196451458058087</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.09106605469441002</v>
+        <v>2.126251268160163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sb300</t>
+          <t>CdS2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,16 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.104671720995331</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.05089960295758991</v>
+        <v>1.270211418526796</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sb400</t>
+          <t>CdS3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -522,16 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.191277916771089</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.09102351330055976</v>
+        <v>1.962366367582087</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sb400</t>
+          <t>CdS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -540,226 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.111695526525509</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.04921159029328564</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mo_25Se_200Sb</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1.129801596051832</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0412271176589978</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mo_25Se_200Sb</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9860919956939599</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0232035051469779</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Mo_125Se_200Sb</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1.134629018804752</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.06335461504731341</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mo_125Se_200Sb</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8897474050259655</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.04254422120919129</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mo_25Se_300Sb</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1.170478039530471</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.06841814052637445</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mo_25Se_300Sb</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9930569202440097</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.04308117309271923</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mo_125Se_300Sb</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1.184143034864894</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0780094018372882</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Mo_125Se_300Sb</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1.047598390089843</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.04900609120275409</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Mo_25Se_400Sb</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1.180588721930234</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.07196233614548796</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mo_25Se_400Sb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1.038327700222461</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.04238852094206078</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Mo_125Se_400Sb</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1.182185036955623</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.07090771464597762</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Mo_125Se_400Sb</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1.03499525750713</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.04085617909626622</v>
+        <v>0.1666805568747302</v>
       </c>
     </row>
   </sheetData>

--- a/UV-Vis/Plots/Summary_Bandgaps.xlsx
+++ b/UV-Vis/Plots/Summary_Bandgaps.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,16 @@
           <t>Gap (eV)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Error (eV)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +450,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.238377246593132</v>
+        <v>1.201084788396404</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09594243273782281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CdS1</t>
+          <t>Sb200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +468,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.424397396537707</v>
+        <v>1.112809405129241</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05358192065359806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CdS2</t>
+          <t>Sb300</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +486,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.126251268160163</v>
+        <v>1.196451458058087</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09106605469441002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CdS2</t>
+          <t>Sb300</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,13 +504,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.270211418526796</v>
+        <v>1.104671720995331</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05089960295758991</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CdS3</t>
+          <t>Sb400</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +522,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.962366367582087</v>
+        <v>1.191277916771089</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09102351330055976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CdS3</t>
+          <t>Sb400</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,7 +540,226 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1666805568747302</v>
+        <v>1.111695526525509</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04921159029328564</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mo_25Se_200Sb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.171970465823233</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07152015822257725</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mo_25Se_200Sb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.99825111719142</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04576085803768118</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mo_125Se_200Sb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.13707211278671</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.06439140746413527</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mo_125Se_200Sb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8846162053495698</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04311096620014647</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mo_25Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.172766847978086</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06771258353971324</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mo_25Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9915019824384799</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04187404018253801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mo_125Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.190433813899426</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.08063638809745149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mo_125Se_300Sb</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.055475434542711</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.04976974656644342</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mo_25Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.167784232448515</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.06887773579631484</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mo_25Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.008958186195559</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.04329792069383679</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mo_125Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.185945856861458</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.07280052537926</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mo_125Se_400Sb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.038339554979267</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.04232129456129601</v>
       </c>
     </row>
   </sheetData>
